--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GUVI\GuviGit\GuviPythonAutomationTesting2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95A3CA5-F730-40C7-87D5-11AFF27817A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89338D52-E3D9-4444-A203-043FEF6F9362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7092" yWindow="2448" windowWidth="13200" windowHeight="6744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>TC_ID 01</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>xyz</t>
+  </si>
+  <si>
+    <t>asdfg</t>
   </si>
 </sst>
 </file>
@@ -345,12 +354,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GUVI\GuviGit\GuviPythonAutomationTesting2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sivan\OneDrive\Documents\Temp\GitApr2026guvi\GuviPythonAutomationTesting2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95A3CA5-F730-40C7-87D5-11AFF27817A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4000CC5D-0FE8-447C-8A09-113B957B46B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7092" yWindow="2448" windowWidth="13200" windowHeight="6744" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>TC_ID 01</t>
+  </si>
+  <si>
+    <t>Test Description</t>
+  </si>
+  <si>
+    <t>Test Step</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
   </si>
 </sst>
 </file>
@@ -345,12 +354,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
